--- a/experiment_results/wu_calibration/rtt_bursts_rps10_att4_WU100000.xlsx
+++ b/experiment_results/wu_calibration/rtt_bursts_rps10_att4_WU100000.xlsx
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -538,22 +538,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -583,34 +583,34 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.3</t>
+          <t>00:030.0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>21782</t>
+          <t>57246</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,22 +652,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>43363</t>
+          <t>85791</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:049.9</t>
+          <t>00:050.1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63741</t>
+          <t>112383</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:060.0</t>
+          <t>00:059.7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75412</t>
+          <t>133306</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.0</t>
+          <t>01:010.1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>90326</t>
+          <t>159038</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.0</t>
+          <t>01:020.1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>111030</t>
+          <t>193406</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:029.7</t>
+          <t>01:029.9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>128500</t>
+          <t>218454</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:039.8</t>
+          <t>01:039.9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>136985</t>
+          <t>242063</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.9</t>
+          <t>01:050.1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>146598</t>
+          <t>272014</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:060.0</t>
+          <t>02:000.1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>160827</t>
+          <t>298923</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.3</t>
+          <t>02:009.7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>173750</t>
+          <t>327100</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.9</t>
+          <t>02:020.0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>185670</t>
+          <t>348837</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.1</t>
+          <t>02:029.9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>198008</t>
+          <t>369389</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:038.6</t>
+          <t>02:038.3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>199335</t>
+          <t>378454</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
@@ -1393,22 +1393,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>190373</t>
+          <t>371668</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1450,22 +1450,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>185839</t>
+          <t>368369</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
